--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486329_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486329_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5291</v>
+        <v>5.7355</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6782</v>
+        <v>4.0387</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8509</v>
+        <v>1.6968</v>
       </c>
       <c r="G2" t="n">
         <v>4.3357</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2193</v>
+        <v>-0.0129</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3929</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5341</v>
+        <v>0.38</v>
       </c>
       <c r="V2" t="n">
         <v>0.7602</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8818</v>
+        <v>3.2855</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8915</v>
+        <v>4.1719</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0097</v>
+        <v>-0.8864</v>
       </c>
       <c r="G3" t="n">
         <v>2.1758</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5533</v>
+        <v>-1.0431</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8843</v>
+        <v>0.1646</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.331</v>
+        <v>-1.2077</v>
       </c>
       <c r="V3" t="n">
         <v>0.1952</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5696</v>
+        <v>3.088</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5314</v>
+        <v>3.5566</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9618</v>
+        <v>-0.4687</v>
       </c>
       <c r="G4" t="n">
         <v>3.7393</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.4748</v>
+        <v>-1.9564</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4879</v>
+        <v>-0.4626</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.9869</v>
+        <v>-1.4937</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2819</v>
+        <v>0.0363</v>
       </c>
       <c r="E5" t="n">
-        <v>2.576</v>
+        <v>3.0483</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8579</v>
+        <v>-3.012</v>
       </c>
       <c r="G5" t="n">
         <v>0.7173</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4989</v>
+        <v>-2.1808</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2329</v>
+        <v>-0.7607</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.266</v>
+        <v>-1.4201</v>
       </c>
       <c r="V5" t="n">
         <v>1.4997</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0386</v>
+        <v>-0.9085</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0987</v>
+        <v>-0.0302</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9399</v>
+        <v>-0.8782</v>
       </c>
       <c r="G6" t="n">
         <v>0.3363</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2449</v>
+        <v>-0.1148</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.137</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5514</v>
+        <v>-1.4867</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3091</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2423</v>
+        <v>-1.5814</v>
       </c>
       <c r="G7" t="n">
         <v>0.9832</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0997</v>
+        <v>-1.035</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3497</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3462</v>
+        <v>-0.6853</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5649999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1858</v>
+        <v>-2.443</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7284</v>
+        <v>-0.3247</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4574</v>
+        <v>-2.1183</v>
       </c>
       <c r="G8" t="n">
         <v>1.6865</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.937</v>
+        <v>-1.1942</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.822</v>
+        <v>-0.4182</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1151</v>
+        <v>-0.776</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7602</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1113</v>
+        <v>-3.8741</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6274</v>
+        <v>-3.2669</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4839</v>
+        <v>-0.6072</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1404</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0808</v>
+        <v>-0.8436</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>-0.5299</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1904</v>
+        <v>-0.3137</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8902</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4656</v>
+        <v>-5.3277</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6026</v>
+        <v>-3.3106</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8631</v>
+        <v>-2.0172</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3236</v>
@@ -1234,13 +1234,13 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6423</v>
+        <v>-0.5044</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.3929</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0427</v>
+        <v>-0.1115</v>
       </c>
       <c r="V10" t="n">
         <v>-2.6297</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6184</v>
+        <v>-5.3504</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6595</v>
+        <v>-6.2989</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0411</v>
+        <v>0.9486</v>
       </c>
       <c r="G11" t="n">
         <v>-1.227</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1288</v>
+        <v>-0.8607</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9589</v>
+        <v>-0.5984</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1698</v>
+        <v>-0.2623</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.272500000000001</v>
+        <v>-7.245099999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6513999999999989</v>
+        <v>1.6789</v>
       </c>
       <c r="F12" t="n">
         <v>-8.923999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>13.0502</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.7732</v>
+        <v>-9.745900000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.8368</v>
+        <v>-3.8092</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.936500000000001</v>
+        <v>-5.9366</v>
       </c>
       <c r="V12" t="n">
         <v>-4.52</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.008</v>
+        <v>4.4781</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1684</v>
+        <v>1.3919</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8396</v>
+        <v>3.0862</v>
       </c>
       <c r="G13" t="n">
         <v>0.6776</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6355</v>
+        <v>1.1056</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1406</v>
+        <v>0.3641</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4949</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.2599</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9009</v>
+        <v>3.9844</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8965</v>
+        <v>2.4631</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0044</v>
+        <v>1.5214</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3096</v>
+        <v>1.1145</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8673</v>
+        <v>0.8547</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4423</v>
+        <v>0.2598</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9374</v>
+        <v>2.2852</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8577</v>
+        <v>1.156</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07969999999999999</v>
+        <v>1.1292</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3722</v>
+        <v>-1.1707</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0096</v>
+        <v>-0.3013</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3626</v>
+        <v>-0.8694</v>
       </c>
       <c r="P14" t="n">
-        <v>0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>1.526</v>
+        <v>0.4774</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0911</v>
+        <v>0.1779</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4349</v>
+        <v>0.2995</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6028</v>
+        <v>3.423</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6808</v>
+        <v>1.4495</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9221</v>
+        <v>1.9736</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1145</v>
+        <v>2.3096</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8547</v>
+        <v>1.8673</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2598</v>
+        <v>0.4423</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2852</v>
+        <v>0.9374</v>
       </c>
       <c r="K15" t="n">
-        <v>1.156</v>
+        <v>0.8577</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1292</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1707</v>
+        <v>1.3722</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3013</v>
+        <v>1.0096</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8694</v>
+        <v>0.3626</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3926</v>
+        <v>0.435</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0958</v>
+        <v>1.0482</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6044</v>
+        <v>0.6441</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7002</v>
+        <v>0.4041</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2619</v>
+        <v>1.6761</v>
       </c>
       <c r="E16" t="n">
-        <v>4.945</v>
+        <v>4.051</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6831</v>
+        <v>-2.3749</v>
       </c>
       <c r="G16" t="n">
         <v>0.4339</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1102</v>
+        <v>1.5244</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0213</v>
+        <v>1.1272</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.3972</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9347</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ALONSO CUEVAS</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4225</v>
+        <v>1.4337</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0208</v>
+        <v>2.3816</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5984</v>
+        <v>-0.9479</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2443</v>
+        <v>2.1404</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0036</v>
+        <v>-0.4988</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2479</v>
+        <v>2.6392</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7224</v>
+        <v>4.8882</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5694</v>
+        <v>0.3166</v>
       </c>
       <c r="L17" t="n">
-        <v>0.153</v>
+        <v>4.5716</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9668</v>
+        <v>-2.7477</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5659</v>
+        <v>-0.8153</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4009</v>
+        <v>-1.9324</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>-3.9151</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2175</v>
+        <v>-5.4377</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1665</v>
+        <v>0.9484</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8857</v>
+        <v>0.4759</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2809</v>
+        <v>0.4726</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9347</v>
+        <v>2.2599</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3698</v>
+        <v>2.4552</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>A. ALONSO CUEVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1293</v>
+        <v>0.8599</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0463</v>
+        <v>1.7973</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.917</v>
+        <v>-0.9374</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1404</v>
+        <v>-0.2443</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4988</v>
+        <v>1.0036</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6392</v>
+        <v>-1.2479</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8882</v>
+        <v>1.7224</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3166</v>
+        <v>1.5694</v>
       </c>
       <c r="L18" t="n">
-        <v>4.5716</v>
+        <v>0.153</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7477</v>
+        <v>-1.9668</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8153</v>
+        <v>-0.5659</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9324</v>
+        <v>-1.4009</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.9151</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.4377</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.644</v>
+        <v>1.604</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1406</v>
+        <v>0.6621</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5034</v>
+        <v>0.9418</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2599</v>
+        <v>-0.9347</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4552</v>
+        <v>-0.3698</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0866</v>
+        <v>-0.1127</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-1.5095</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5499000000000001</v>
+        <v>1.3968</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.7812</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2645</v>
+        <v>-0.727</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7913</v>
+        <v>-0.0542</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7068</v>
+        <v>-0.5938</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.7086</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7068</v>
+        <v>0.1147</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1801</v>
+        <v>-0.1873</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2645</v>
+        <v>-0.0184</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.1689</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2449</v>
+        <v>0.4509</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.125</v>
+        <v>0.1719</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3699</v>
+        <v>0.2791</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8873</v>
+        <v>-0.1483</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0683</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1.181</v>
+        <v>0.4883</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7812</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.727</v>
+        <v>0.2645</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0542</v>
+        <v>-0.7913</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5938</v>
+        <v>-0.7068</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7086</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1147</v>
+        <v>-0.7068</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1873</v>
+        <v>0.1801</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0184</v>
+        <v>0.2645</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1689</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3236</v>
+        <v>0.1833</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3869</v>
+        <v>-0.125</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0633</v>
+        <v>0.3082</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.081</v>
+        <v>-1.0194</v>
       </c>
       <c r="E21" t="n">
         <v>-0.911</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1701</v>
+        <v>-0.1084</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9732</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9352</v>
+        <v>0.9968</v>
       </c>
       <c r="T21" t="n">
         <v>0.8857</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0495</v>
+        <v>0.1111</v>
       </c>
       <c r="V21" t="n">
         <v>1.3045</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7715</v>
+        <v>-1.2147</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0493</v>
+        <v>0.2918</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7223</v>
+        <v>-1.5065</v>
       </c>
       <c r="G22" t="n">
         <v>-3.282</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6216</v>
+        <v>0.9352</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0959</v>
+        <v>0.2452</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4743</v>
+        <v>0.6901</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3904</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2263</v>
+        <v>-5.0876</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1687</v>
+        <v>-1.8451</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0575</v>
+        <v>-3.2425</v>
       </c>
       <c r="G23" t="n">
         <v>-8.1517</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3604</v>
+        <v>1.4991</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9838</v>
+        <v>1.3075</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3766</v>
+        <v>0.1917</v>
       </c>
       <c r="V23" t="n">
         <v>1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.272699999999999</v>
+        <v>8.272499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>8.9239</v>
+        <v>8.923999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6514000000000006</v>
+        <v>-0.6513000000000004</v>
       </c>
       <c r="G24" t="n">
         <v>-10.2831</v>
@@ -2329,7 +2329,7 @@
         <v>10.7733</v>
       </c>
       <c r="T24" t="n">
-        <v>5.9366</v>
+        <v>5.936599999999999</v>
       </c>
       <c r="U24" t="n">
         <v>4.8368</v>
